--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEVADA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/NEVADA_2014.xlsx
@@ -2562,7 +2562,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C123">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C290">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C300">
@@ -13776,7 +13776,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C746">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C827">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C858">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C864">
@@ -16638,7 +16638,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C905">
@@ -22236,7 +22236,7 @@
       </c>
       <c r="B1216" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C1216">
@@ -24810,7 +24810,7 @@
       </c>
       <c r="B1359" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1359">
